--- a/data/trending_integrated_20260911_15.xlsx
+++ b/data/trending_integrated_20260911_15.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2720</v>
+        <v>16060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.83%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.04</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>420</v>
+        <v>186</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2095</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>2090</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>2720</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>2080</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>8138449364</v>
+        <v>208461822905</v>
       </c>
       <c r="P2" t="n">
-        <v>8150</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>376</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 양자 보안 기술 상용화 기대감. 관련 뉴스와 공시 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['양자 보안', '사이버 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16060</v>
+        <v>2720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+29.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>174</v>
+        <v>426</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>1.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12610</v>
+        <v>2095</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>208383000000</v>
+        <v>8141438644</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>8150</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="R3" t="n">
-        <v>-71000</v>
+        <v>219000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 엑스게이트 급등 기대감, 양자 보안 기술 상용화 성공.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['젠슨 황', '사이버 보안', '양자 보안']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2625</v>
+        <v>2620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.53%</t>
+          <t>+23.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -794,7 +794,7 @@
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>123940430128</v>
+        <v>125468648378</v>
       </c>
       <c r="P4" t="n">
         <v>4810</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>개미 투자자만 많고 힘이 없는 모습, 외국인 및 법인 대량 매도 추정.</t>
+          <t>거래량 증가에도 불구하고 주가 상승 동력 부재에 대한 우려. 외국인 및 기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['개미 투자자', '외국인 매도', '거래량']</t>
+          <t>['거래량', '매도세', '테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15980</v>
+        <v>15790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.43%</t>
+          <t>+18.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.19</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F5" t="n">
         <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H5" t="n">
         <v>1.24</v>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13160</v>
+        <v>13340</v>
       </c>
       <c r="K5" t="n">
-        <v>12910</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16920</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>12910</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>174855941895</v>
+        <v>178584000000</v>
       </c>
       <c r="P5" t="n">
-        <v>61700</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속. 경영권 및 금리 인상 관련 언급.</t>
+          <t>K-뷰티 대장주로서의 상승세 기대감. 외인 기관 매수세 유입 및 경영권 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['K-뷰티', '급등세', '경영권']</t>
+          <t>['K-뷰티', '경영권', '외인 기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138200</v>
+        <v>137000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.45%</t>
+          <t>+17.80%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H6" t="n">
         <v>4.32</v>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>115700</v>
+        <v>116300</v>
       </c>
       <c r="K6" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>519305080300</v>
+        <v>527220000000</v>
       </c>
       <c r="P6" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>39000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상품 부족으로 인한 판매 호조 기대감, 높은 변동성과 거래량 부족에 대한 우려.</t>
+          <t>반도체 부품 품절 이슈 및 주가 상승 기대감. 거래량 부진에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['판매 호조', '거래량', '변동성']</t>
+          <t>['반도체 부품', '품절', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7210</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.61%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.79</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F7" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>403</v>
+        <v>519</v>
       </c>
       <c r="H7" t="n">
-        <v>2.15</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>172831054340</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>170000</v>
+        <v>45000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>광통신&amp;위성네트워크 액티브 펀드 편입, 대장주로서의 기대감과 함께 힘없는 모습도 관찰됨.</t>
+          <t>신영 창구 매물 및 대차 증가에 대한 우려, 금호타이어 주가 상승 기대감과 지루한 공방전.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['신영 창구', '대차', '금호타이어']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9970</v>
+        <v>7190</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+7.31%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>337</v>
+        <v>415</v>
       </c>
       <c r="H8" t="n">
-        <v>4.49</v>
+        <v>2.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9280</v>
+        <v>6700</v>
       </c>
       <c r="K8" t="n">
-        <v>10030</v>
+        <v>6530</v>
       </c>
       <c r="L8" t="n">
-        <v>10880</v>
+        <v>8370</v>
       </c>
       <c r="M8" t="n">
-        <v>9800</v>
+        <v>6430</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>22251887175</v>
+        <v>173866071275</v>
       </c>
       <c r="P8" t="n">
-        <v>15640</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>5470</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>-88000</v>
+        <v>170000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>광통신 및 위성 네트워크 섹터 내 대장주로서의 기대감. 공매도 물량 증가 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['광통신', '위성 네트워크', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1890</v>
+        <v>9920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.39%</t>
+          <t>+6.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>4.49</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1760</v>
+        <v>9280</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>4.42</v>
       </c>
       <c r="O9" t="n">
-        <v>45164000000</v>
+        <v>22417042510</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R9" t="n">
-        <v>-445000</v>
+        <v>-88000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주로서의 부각. VLCC 부유식 저장고 용선료 폭등 언급.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['홍해 사태', '전쟁 테마주', '유가 급등']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,95 +1287,95 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14770</v>
+        <v>19980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.11</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>489</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>267</v>
+        <v>94</v>
       </c>
       <c r="G10" t="n">
-        <v>1068</v>
+        <v>622</v>
       </c>
       <c r="H10" t="n">
-        <v>3.14</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14510</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>14600</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>213914931155</v>
+        <v>144794000000</v>
       </c>
       <c r="P10" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-339000</v>
+        <v>28000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
+          <t>대차 해지 및 공매도 세력에 대한 경고. 원전 사업 투자 기대감 및 목표가 상향 뉴스 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
+          <t>['대차 해지', '공매도', '원전 사업']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7790</v>
+        <v>8450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>285</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="G11" t="n">
-        <v>149</v>
+        <v>1414</v>
       </c>
       <c r="H11" t="n">
-        <v>0.52</v>
+        <v>1.29</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7690</v>
+        <v>8300</v>
       </c>
       <c r="K11" t="n">
-        <v>7670</v>
+        <v>8400</v>
       </c>
       <c r="L11" t="n">
-        <v>9170</v>
+        <v>8700</v>
       </c>
       <c r="M11" t="n">
-        <v>7450</v>
+        <v>7540</v>
       </c>
       <c r="N11" t="n">
-        <v>0.46</v>
+        <v>1.17</v>
       </c>
       <c r="O11" t="n">
-        <v>88939171225</v>
+        <v>34161790860</v>
       </c>
       <c r="P11" t="n">
-        <v>9170</v>
+        <v>21500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3720</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>14000</v>
+        <v>-183000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락 및 거래량 부진에 대한 불안감. 594억 공급 계약 관련 사실 언급.</t>
+          <t>페니트리움 임상 시험 디자인 및 파이프라인 로드맵 언급. 9월 14일 WCLC 학회 이후 주가 대폭등 예고 및 외국계 증권사 매수 동향.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '거래량', '공급 계약']</t>
+          <t>['페니트리움', '임상시험', 'WCLC']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51000</v>
+        <v>3875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>-0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>644</v>
+        <v>217</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50400</v>
+        <v>3810</v>
       </c>
       <c r="K12" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>82219868725</v>
+        <v>97959000000</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-172000</v>
+        <v>-560000</v>
       </c>
       <c r="S12" t="n">
-        <v>64000</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시', '삼성']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19980</v>
+        <v>51000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G13" t="n">
-        <v>583</v>
+        <v>657</v>
       </c>
       <c r="H13" t="n">
-        <v>10.65</v>
+        <v>38.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19750</v>
+        <v>50400</v>
       </c>
       <c r="K13" t="n">
-        <v>19500</v>
+        <v>50500</v>
       </c>
       <c r="L13" t="n">
-        <v>20150</v>
+        <v>51300</v>
       </c>
       <c r="M13" t="n">
-        <v>19060</v>
+        <v>49650</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>38.69</v>
       </c>
       <c r="O13" t="n">
-        <v>139560601095</v>
+        <v>83861211425</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>28000</v>
+        <v>-172000</v>
       </c>
       <c r="S13" t="n">
-        <v>-43000</v>
+        <v>64000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['수주', '공시', '삼성']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52300</v>
+        <v>14660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.44</v>
+        <v>3.11</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>501</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>273</v>
       </c>
       <c r="G14" t="n">
-        <v>212</v>
+        <v>1077</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51800</v>
+        <v>14510</v>
       </c>
       <c r="K14" t="n">
-        <v>51300</v>
+        <v>17010</v>
       </c>
       <c r="L14" t="n">
-        <v>54500</v>
+        <v>17310</v>
       </c>
       <c r="M14" t="n">
-        <v>51300</v>
+        <v>14600</v>
       </c>
       <c r="N14" t="n">
-        <v>3.36</v>
+        <v>0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>106915198300</v>
+        <v>216490992180</v>
       </c>
       <c r="P14" t="n">
-        <v>87700</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>17210</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>127000</v>
+        <v>-339000</v>
       </c>
       <c r="S14" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90500</v>
+        <v>52000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>-0.44</v>
       </c>
       <c r="E15" t="n">
-        <v>255</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>981</v>
+        <v>222</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89900</v>
+        <v>51800</v>
       </c>
       <c r="K15" t="n">
-        <v>88700</v>
+        <v>51300</v>
       </c>
       <c r="L15" t="n">
-        <v>91100</v>
+        <v>54500</v>
       </c>
       <c r="M15" t="n">
-        <v>88000</v>
+        <v>51300</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>3.36</v>
       </c>
       <c r="O15" t="n">
-        <v>191229479400</v>
+        <v>110067037950</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>87700</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>17210</v>
       </c>
       <c r="R15" t="n">
-        <v>-313000</v>
+        <v>127000</v>
       </c>
       <c r="S15" t="n">
-        <v>77000</v>
+        <v>34000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 29조 7천억 규모 기반 상승 기대.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지', '수주잔고', '원전']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H16" t="n">
         <v>38.02</v>
@@ -1898,7 +1898,7 @@
         <v>37.82</v>
       </c>
       <c r="O16" t="n">
-        <v>70496059250</v>
+        <v>72809446250</v>
       </c>
       <c r="P16" t="n">
         <v>822000</v>
@@ -1951,20 +1951,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="H17" t="n">
         <v>27.19</v>
@@ -1975,28 +1975,28 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8970</v>
+        <v>8950</v>
       </c>
       <c r="K17" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8950</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>20282881375</v>
+        <v>20821000000</v>
       </c>
       <c r="P17" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>-8000</v>
@@ -2035,267 +2035,267 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3885</v>
+        <v>1892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.53</v>
+        <v>0.32</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3925</v>
+        <v>1901</v>
       </c>
       <c r="K18" t="n">
-        <v>3810</v>
+        <v>2050</v>
       </c>
       <c r="L18" t="n">
-        <v>4180</v>
+        <v>2080</v>
       </c>
       <c r="M18" t="n">
-        <v>3760</v>
+        <v>1880</v>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>96834316971</v>
+        <v>45692327001</v>
       </c>
       <c r="P18" t="n">
-        <v>8100</v>
+        <v>4795</v>
       </c>
       <c r="Q18" t="n">
-        <v>592</v>
+        <v>1524</v>
       </c>
       <c r="R18" t="n">
-        <v>-560000</v>
+        <v>-445000</v>
       </c>
       <c r="S18" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25700</v>
+        <v>29550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32</v>
+        <v>25.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>26100</v>
+        <v>29800</v>
       </c>
       <c r="K19" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.33</v>
+        <v>24.99</v>
       </c>
       <c r="O19" t="n">
-        <v>343075524800</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2000</v>
+        <v>599000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-270000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '탈출 기회', '외인 유입']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1822000</v>
+        <v>7850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>126</v>
       </c>
       <c r="F20" t="n">
-        <v>441</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>2115</v>
+        <v>154</v>
       </c>
       <c r="H20" t="n">
-        <v>50.55</v>
+        <v>0.52</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1853000</v>
+        <v>7990</v>
       </c>
       <c r="K20" t="n">
-        <v>1773000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1827000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1768000</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>50.67</v>
+        <v>0.46</v>
       </c>
       <c r="O20" t="n">
-        <v>4070626802000</v>
+        <v>89434000000</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>305500</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-393000</v>
+        <v>14000</v>
       </c>
       <c r="S20" t="n">
-        <v>-178000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기관 매수세와 계단식 상승 기대, 중동 평화 회담 및 CPI 발표 변수 고려.</t>
+          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['기관 매수', '계단식 상승', 'CPI 발표']</t>
+          <t>['품절주', '주가 조정', '유통 물량']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14770</v>
+        <v>14750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>24030131180</v>
+        <v>24441356055</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2367,7 +2367,7 @@
         <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2403,123 +2403,123 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3550</v>
+        <v>89900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="G22" t="n">
-        <v>170</v>
+        <v>989</v>
       </c>
       <c r="H22" t="n">
-        <v>0.73</v>
+        <v>23.59</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3620</v>
+        <v>91700</v>
       </c>
       <c r="K22" t="n">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3915</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3520</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>23.65</v>
       </c>
       <c r="O22" t="n">
-        <v>48742078642</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-110000</v>
+        <v>-313000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>에너지 대미 투자 협상 마무리 및 원전 사업 수주 기대감. WSJ 보도 인용 및 수주 잔고 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['두산에너빌리티', '원전', '수주잔고']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28900</v>
+        <v>1817000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>453</v>
       </c>
       <c r="G23" t="n">
-        <v>179</v>
+        <v>2060</v>
       </c>
       <c r="H23" t="n">
-        <v>51.44</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,183 +2527,183 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29550</v>
+        <v>1856000</v>
       </c>
       <c r="K23" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>29050</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>24.99</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>57882792450</v>
+        <v>4139152000000</v>
       </c>
       <c r="P23" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>599000</v>
+        <v>-393000</v>
       </c>
       <c r="S23" t="n">
-        <v>-270000</v>
+        <v>-178000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>계단식 상승 추세 기대감 및 기관 매수세 유입. 중동 평화 회담 및 유가 하락 등 거시 경제 지표 변화 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['계단식 상승', '기관 매수', '거시 경제']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8080</v>
+        <v>193300</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>269</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>1359</v>
+        <v>172</v>
       </c>
       <c r="H24" t="n">
-        <v>1.29</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8300</v>
+        <v>197500</v>
       </c>
       <c r="K24" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.17</v>
+        <v>75.92</v>
       </c>
       <c r="O24" t="n">
-        <v>31827933265</v>
+        <v>541602000000</v>
       </c>
       <c r="P24" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-183000</v>
+        <v>-1193000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>임상 시험 디자인 공개 및 학회 발표 임박에 따른 주가 상승 기대감.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['임상 시험', '학회', '외인']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12230</v>
+        <v>25500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E25" t="n">
-        <v>113</v>
+        <v>366</v>
       </c>
       <c r="F25" t="n">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="G25" t="n">
-        <v>118</v>
+        <v>567</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,222 +2711,222 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12630</v>
+        <v>26100</v>
       </c>
       <c r="K25" t="n">
-        <v>12520</v>
+        <v>26350</v>
       </c>
       <c r="L25" t="n">
-        <v>12930</v>
+        <v>30300</v>
       </c>
       <c r="M25" t="n">
-        <v>11900</v>
+        <v>25300</v>
       </c>
       <c r="N25" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>66793102040</v>
+        <v>347045666900</v>
       </c>
       <c r="P25" t="n">
-        <v>20850</v>
+        <v>39350</v>
       </c>
       <c r="Q25" t="n">
-        <v>4020</v>
+        <v>8200</v>
       </c>
       <c r="R25" t="n">
-        <v>-105000</v>
+        <v>2000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['주포', '탈출 기회', '외인 유입']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>260000</v>
+        <v>3535</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>1766</v>
+        <v>172</v>
       </c>
       <c r="H26" t="n">
-        <v>46.71</v>
+        <v>0.73</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>269000</v>
+        <v>3620</v>
       </c>
       <c r="K26" t="n">
-        <v>258000</v>
+        <v>3725</v>
       </c>
       <c r="L26" t="n">
-        <v>261500</v>
+        <v>3915</v>
       </c>
       <c r="M26" t="n">
-        <v>256500</v>
+        <v>3520</v>
       </c>
       <c r="N26" t="n">
-        <v>46.81</v>
+        <v>1.54</v>
       </c>
       <c r="O26" t="n">
-        <v>3070978608500</v>
+        <v>49269130611</v>
       </c>
       <c r="P26" t="n">
-        <v>374500</v>
+        <v>4335</v>
       </c>
       <c r="Q26" t="n">
-        <v>72100</v>
+        <v>1246</v>
       </c>
       <c r="R26" t="n">
-        <v>-2983000</v>
+        <v>-110000</v>
       </c>
       <c r="S26" t="n">
-        <v>-1179000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>이재명 재판 재개 시 상승 기대감, 네이버 증권 게시판 불만 제기. 외인 비중 변화는 미미.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['이재명', '증권 게시판', '이부진']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14050</v>
+        <v>259500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>127</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>498</v>
       </c>
       <c r="G27" t="n">
-        <v>718</v>
+        <v>1766</v>
       </c>
       <c r="H27" t="n">
-        <v>5.98</v>
+        <v>46.71</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14600</v>
+        <v>269000</v>
       </c>
       <c r="K27" t="n">
-        <v>14800</v>
+        <v>258000</v>
       </c>
       <c r="L27" t="n">
-        <v>14950</v>
+        <v>261500</v>
       </c>
       <c r="M27" t="n">
-        <v>13910</v>
+        <v>256500</v>
       </c>
       <c r="N27" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="O27" t="n">
-        <v>117835075660</v>
+        <v>3131035541000</v>
       </c>
       <c r="P27" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q27" t="n">
-        <v>3540</v>
+        <v>72100</v>
       </c>
       <c r="R27" t="n">
-        <v>-236000</v>
+        <v>-2983000</v>
       </c>
       <c r="S27" t="n">
-        <v>-163000</v>
+        <v>-1179000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원전 관련 언급과 함께 일부 매수세 유입 기대.</t>
+          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['원전', '매수세', '120일선']</t>
+          <t>['반도체', '주가 부진', '증권 뉴스']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,77 +2948,77 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7390</v>
+        <v>14160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="F28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" t="n">
-        <v>514</v>
+        <v>459</v>
       </c>
       <c r="H28" t="n">
-        <v>11.72</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>7680</v>
+        <v>14740</v>
       </c>
       <c r="K28" t="n">
-        <v>7540</v>
+        <v>14050</v>
       </c>
       <c r="L28" t="n">
-        <v>7660</v>
+        <v>14560</v>
       </c>
       <c r="M28" t="n">
-        <v>7340</v>
+        <v>14030</v>
       </c>
       <c r="N28" t="n">
-        <v>11.62</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>11701786120</v>
+        <v>66717177375</v>
       </c>
       <c r="P28" t="n">
-        <v>8850</v>
+        <v>31500</v>
       </c>
       <c r="Q28" t="n">
-        <v>4220</v>
+        <v>1272</v>
       </c>
       <c r="R28" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>신영 창구 매물 및 대차 증가에 대한 우려, 금호타이어 주가 상승 기대감과 지루한 공방전.</t>
+          <t>대한민국 주식 시장에 대한 부정적 언급과 함께 향후 상승 기대감 표현. 오라클 순이익 급증 및 금리 인상 언급.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['신영 창구', '대차', '금호타이어']</t>
+          <t>['대한광통신', '금리인상', '오라클']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,38 +3040,38 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14180</v>
+        <v>14020</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-3.80%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="E29" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F29" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G29" t="n">
-        <v>447</v>
+        <v>726</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5</v>
+        <v>5.98</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3079,51 +3079,51 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14740</v>
+        <v>14600</v>
       </c>
       <c r="K29" t="n">
-        <v>14050</v>
+        <v>14800</v>
       </c>
       <c r="L29" t="n">
-        <v>14560</v>
+        <v>14950</v>
       </c>
       <c r="M29" t="n">
-        <v>14030</v>
+        <v>13910</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="O29" t="n">
-        <v>65284882750</v>
+        <v>119831835320</v>
       </c>
       <c r="P29" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q29" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R29" t="n">
-        <v>-303000</v>
+        <v>-236000</v>
       </c>
       <c r="S29" t="n">
-        <v>-28000</v>
+        <v>-163000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>정치적 요인과 금리 인상 관련 언급이 있으며, 우리로 종목과의 비교 및 매수 기회에 대한 논의가 있음.</t>
+          <t>원전 관련 언급 다수, 일부 투자자들은 긍정적 전망. 모건 등 기관 매매 동향 언급.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['정치', '금리', '매수']</t>
+          <t>['원전', '120일선', '모건']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3132,77 +3132,77 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>193600</v>
+        <v>12220</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-4.63%</t>
+          <t>-6.22%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F30" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G30" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="H30" t="n">
-        <v>75.98999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>203000</v>
+        <v>13030</v>
       </c>
       <c r="K30" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>75.92</v>
+        <v>0.14</v>
       </c>
       <c r="O30" t="n">
-        <v>529600279300</v>
+        <v>68550000000</v>
       </c>
       <c r="P30" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-1193000</v>
+        <v>-105000</v>
       </c>
       <c r="S30" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -3246,13 +3246,13 @@
         <v>-0.96</v>
       </c>
       <c r="E31" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F31" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G31" t="n">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="H31" t="n">
         <v>7.58</v>
@@ -3278,7 +3278,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>232684748000</v>
+        <v>236628127500</v>
       </c>
       <c r="P31" t="n">
         <v>426000</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>공매도 세력과의 공방이 치열한 가운데, 주가 하락에 대한 우려와 함께 매수 후 소각 등 주주 가치 제고 방안에 대한 요구가 나타나고 있음.</t>
+          <t>공매도 세력에 대한 불만과 주가 하락에 대한 우려 표현. TC 본더 수출 데이터 및 기관 매수세 언급.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '매수 소각']</t>
+          <t>['한미반도체', '공매도', 'TC본더']</t>
         </is>
       </c>
       <c r="X31" t="n">

--- a/data/trending_integrated_20260911_15.xlsx
+++ b/data/trending_integrated_20260911_15.xlsx
@@ -584,7 +584,7 @@
         <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208461822905</v>
+        <v>208537899125</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>-71000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 양자 보안 기술 상용화 기대감. 관련 뉴스와 공시 언급.</t>
+          <t>젠슨 황 발언 기반 AI 다음 핵심 시장으로 사이버 보안 부상. 엑스게이트의 양자 보안 기술 상용화 및 공급 계약 공시로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자 보안', '사이버 보안', '젠슨 황']</t>
+          <t>['양자보안', '사이버보안', '젠슨황']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="H3" t="n">
         <v>1.32</v>
@@ -702,7 +702,7 @@
         <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>8141438644</v>
+        <v>8156975284</v>
       </c>
       <c r="P3" t="n">
         <v>8150</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>2615</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.29%</t>
+          <t>+22.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>125468648378</v>
+        <v>127710000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-1952000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>거래량 증가에도 불구하고 주가 상승 동력 부재에 대한 우려. 외국인 및 기관 매도세 관찰.</t>
+          <t>거래량은 증가하나 종목 자체의 힘 부족으로 상승 동력 약화. 외국인 매도세 출현.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['거래량', '매도세', '테마주']</t>
+          <t>['거래량', '매도세', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,39 +839,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15790</v>
+        <v>14610</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.37%</t>
+          <t>+20.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.19</v>
+        <v>3.11</v>
       </c>
       <c r="E5" t="n">
-        <v>139</v>
+        <v>514</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="G5" t="n">
-        <v>199</v>
+        <v>1079</v>
       </c>
       <c r="H5" t="n">
-        <v>1.24</v>
+        <v>3.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>12090</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.43</v>
+        <v>0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>178584000000</v>
+        <v>219004000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,14 +895,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-339000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주로서의 상승세 기대감. 외인 기관 매수세 유입 및 경영권 관련 내용 언급.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['K-뷰티', '경영권', '외인 기관']</t>
+          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137000</v>
+        <v>137200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.80%</t>
+          <t>+17.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G6" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H6" t="n">
         <v>4.32</v>
@@ -978,7 +978,7 @@
         <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>527220000000</v>
+        <v>535004000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>15710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+17.77%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>519</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>1.24</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>13340</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>181822000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신영 창구 매물 및 대차 증가에 대한 우려, 금호타이어 주가 상승 기대감과 지루한 공방전.</t>
+          <t>K-뷰티 대장주 등극 기대감 속 개인 투자자 중심의 상승세 전망. 다만, 외인/기관 매수에도 얇은 호가창 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신영 창구', '대차', '금호타이어']</t>
+          <t>['K-뷰티', '대장주', '호가창']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7190</v>
+        <v>7210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.31%</t>
+          <t>+9.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
         <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K8" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>173866071275</v>
+        <v>175473000000</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>170000</v>
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9920</v>
+        <v>7680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.90%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>342</v>
+        <v>520</v>
       </c>
       <c r="H9" t="n">
-        <v>4.49</v>
+        <v>11.72</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9280</v>
+        <v>7100</v>
       </c>
       <c r="K9" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.42</v>
+        <v>11.62</v>
       </c>
       <c r="O9" t="n">
-        <v>22417042510</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-88000</v>
+        <v>45000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>신영 창구 매물 및 대차 증가에 대한 우려, 금호타이어 주가 상승 기대감과 지루한 공방전.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['신영 창구', '대차', '금호타이어']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19980</v>
+        <v>1878</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>+6.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E10" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>622</v>
+        <v>264</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>1760</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>144794000000</v>
+        <v>46641000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,27 +1355,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>28000</v>
+        <v>-445000</v>
       </c>
       <c r="S10" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 및 공매도 세력에 대한 경고. 원전 사업 투자 기대감 및 목표가 상향 뉴스 언급.</t>
+          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '원전 사업']</t>
+          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.12</v>
+        <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="F11" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>1414</v>
+        <v>956</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>7.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8300</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>34161790860</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-183000</v>
+        <v>-485000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>페니트리움 임상 시험 디자인 및 파이프라인 로드맵 언급. 9월 14일 WCLC 학회 이후 주가 대폭등 예고 및 외국계 증권사 매수 동향.</t>
+          <t>공매도 세력의 거센 압박 속에서 주가 하락. 개미 투자자 매수세 미흡 및 기관의 제한적 매수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['페니트리움', '임상시험', 'WCLC']</t>
+          <t>['공매도', '개미', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3875</v>
+        <v>90600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>261</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="G12" t="n">
-        <v>217</v>
+        <v>1009</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>89900</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>91100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.57</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>97959000000</v>
+        <v>198178706700</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-560000</v>
+        <v>-313000</v>
       </c>
       <c r="S12" t="n">
-        <v>14000</v>
+        <v>77000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>한국-미국 에너지 투자 협상 타결 및 대규모 수주 잔고 기반 원전 사업 수혜 기대감. WSJ 보도 및 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51000</v>
+        <v>19890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="H13" t="n">
-        <v>38.78</v>
+        <v>10.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50400</v>
+        <v>19750</v>
       </c>
       <c r="K13" t="n">
-        <v>50500</v>
+        <v>19500</v>
       </c>
       <c r="L13" t="n">
-        <v>51300</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>49650</v>
+        <v>19060</v>
       </c>
       <c r="N13" t="n">
-        <v>38.69</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>83861211425</v>
+        <v>150563293750</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-172000</v>
+        <v>28000</v>
       </c>
       <c r="S13" t="n">
-        <v>64000</v>
+        <v>-43000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
+          <t>대차 해지 및 공매도 세력에 대한 경고. 원전 사업 투자 기대감 및 목표가 상향 뉴스 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '공시', '삼성']</t>
+          <t>['대차 해지', '공매도', '원전 사업']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,222 +1660,222 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14660</v>
+        <v>416000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.11</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>501</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>273</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>1077</v>
+        <v>311</v>
       </c>
       <c r="H14" t="n">
-        <v>3.14</v>
+        <v>38.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14510</v>
+        <v>415500</v>
       </c>
       <c r="K14" t="n">
-        <v>17010</v>
+        <v>407000</v>
       </c>
       <c r="L14" t="n">
-        <v>17310</v>
+        <v>418500</v>
       </c>
       <c r="M14" t="n">
-        <v>14600</v>
+        <v>404000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03</v>
+        <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>216490992180</v>
+        <v>75302296250</v>
       </c>
       <c r="P14" t="n">
-        <v>36200</v>
+        <v>822000</v>
       </c>
       <c r="Q14" t="n">
-        <v>8920</v>
+        <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>-339000</v>
+        <v>31000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52000</v>
+        <v>8300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.44</v>
+        <v>0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>101</v>
+        <v>316</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="G15" t="n">
-        <v>222</v>
+        <v>1499</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>1.29</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51800</v>
+        <v>8300</v>
       </c>
       <c r="K15" t="n">
-        <v>51300</v>
+        <v>8400</v>
       </c>
       <c r="L15" t="n">
-        <v>54500</v>
+        <v>8700</v>
       </c>
       <c r="M15" t="n">
-        <v>51300</v>
+        <v>7540</v>
       </c>
       <c r="N15" t="n">
-        <v>3.36</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>110067037950</v>
+        <v>36666251160</v>
       </c>
       <c r="P15" t="n">
-        <v>87700</v>
+        <v>21500</v>
       </c>
       <c r="Q15" t="n">
-        <v>17210</v>
+        <v>2300</v>
       </c>
       <c r="R15" t="n">
-        <v>127000</v>
+        <v>-183000</v>
       </c>
       <c r="S15" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>페니트리움 임상 시험 디자인 및 파이프라인 로드맵 언급. 9월 14일 WCLC 학회 이후 주가 대폭등 예고 및 외국계 증권사 매수 동향.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['페니트리움', '임상시험', 'WCLC']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>415500</v>
+        <v>8940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="H16" t="n">
-        <v>38.02</v>
+        <v>27.19</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>415500</v>
+        <v>8970</v>
       </c>
       <c r="K16" t="n">
-        <v>407000</v>
+        <v>8780</v>
       </c>
       <c r="L16" t="n">
-        <v>418500</v>
+        <v>8950</v>
       </c>
       <c r="M16" t="n">
-        <v>404000</v>
+        <v>8680</v>
       </c>
       <c r="N16" t="n">
-        <v>37.82</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>72809446250</v>
+        <v>21644951220</v>
       </c>
       <c r="P16" t="n">
-        <v>822000</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>283000</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>31000</v>
+        <v>-8000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>-241000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8940</v>
+        <v>50400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>317</v>
+        <v>661</v>
       </c>
       <c r="H17" t="n">
-        <v>27.19</v>
+        <v>38.78</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8950</v>
+        <v>50800</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>27.16</v>
+        <v>38.69</v>
       </c>
       <c r="O17" t="n">
-        <v>20821000000</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,23 +1999,23 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-8000</v>
+        <v>-172000</v>
       </c>
       <c r="S17" t="n">
-        <v>-241000</v>
+        <v>64000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['수주', '공시', '삼성']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,104 +2023,104 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1892</v>
+        <v>3870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.32</v>
+        <v>-0.53</v>
       </c>
       <c r="E18" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1901</v>
+        <v>3925</v>
       </c>
       <c r="K18" t="n">
-        <v>2050</v>
+        <v>3810</v>
       </c>
       <c r="L18" t="n">
-        <v>2080</v>
+        <v>4180</v>
       </c>
       <c r="M18" t="n">
-        <v>1880</v>
+        <v>3760</v>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>45692327001</v>
+        <v>99172362539</v>
       </c>
       <c r="P18" t="n">
-        <v>4795</v>
+        <v>8100</v>
       </c>
       <c r="Q18" t="n">
-        <v>1524</v>
+        <v>592</v>
       </c>
       <c r="R18" t="n">
-        <v>-445000</v>
+        <v>-560000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29550</v>
+        <v>29000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,10 +2148,10 @@
         <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H19" t="n">
-        <v>25.55</v>
+        <v>51.46</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,28 +2159,28 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29800</v>
+        <v>29550</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>28650</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>29050</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="N19" t="n">
         <v>24.99</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>60123690225</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="R19" t="n">
         <v>599000</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7850</v>
+        <v>25600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>126</v>
+        <v>374</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="G20" t="n">
-        <v>154</v>
+        <v>578</v>
       </c>
       <c r="H20" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7990</v>
+        <v>26100</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="N20" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>89434000000</v>
+        <v>350885932200</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
+          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['품절주', '주가 조정', '유통 물량']</t>
+          <t>['주포', '탈출 기회', '외인 유입']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14750</v>
+        <v>1812000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>455</v>
       </c>
       <c r="G21" t="n">
-        <v>351</v>
+        <v>2095</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>50.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,99 +2343,99 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15040</v>
+        <v>1856000</v>
       </c>
       <c r="K21" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>24441356055</v>
+        <v>4225538000000</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>이란-미국 회담 및 휴전 선언 등 지정학적 이벤트에 따른 유가 하락 및 반도체 섹터 회복 기대감. AI 시대 반도체 필수론 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['AI', '반도체', '지정학적']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>89900</v>
+        <v>7800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>256</v>
+        <v>125</v>
       </c>
       <c r="F22" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
-        <v>989</v>
+        <v>153</v>
       </c>
       <c r="H22" t="n">
-        <v>23.59</v>
+        <v>0.52</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>91700</v>
+        <v>7990</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>23.65</v>
+        <v>0.46</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>90003000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,27 +2459,27 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-313000</v>
+        <v>14000</v>
       </c>
       <c r="S22" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 원전 사업 수주 기대감. WSJ 보도 인용 및 수주 잔고 관련 긍정적 전망.</t>
+          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['두산에너빌리티', '원전', '수주잔고']</t>
+          <t>['품절주', '주가 조정', '유통 물량']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1817000</v>
+        <v>51800</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.10%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.12</v>
+        <v>-0.44</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
-        <v>453</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>2060</v>
+        <v>229</v>
       </c>
       <c r="H23" t="n">
-        <v>50.55</v>
+        <v>2.92</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1856000</v>
+        <v>53200</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50.67</v>
+        <v>3.36</v>
       </c>
       <c r="O23" t="n">
-        <v>4139152000000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2551,106 +2551,106 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-393000</v>
+        <v>127000</v>
       </c>
       <c r="S23" t="n">
-        <v>-178000</v>
+        <v>34000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>계단식 상승 추세 기대감 및 기관 매수세 유입. 중동 평화 회담 및 유가 하락 등 거시 경제 지표 변화 언급.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['계단식 상승', '기관 매수', '거시 경제']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>193300</v>
+        <v>3515</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H24" t="n">
-        <v>75.98999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>197500</v>
+        <v>3620</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3507</v>
       </c>
       <c r="N24" t="n">
-        <v>75.92</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>541602000000</v>
+        <v>50167741605</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R24" t="n">
-        <v>-1193000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25500</v>
+        <v>260000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>172</v>
+        <v>497</v>
       </c>
       <c r="G25" t="n">
-        <v>567</v>
+        <v>1793</v>
       </c>
       <c r="H25" t="n">
-        <v>0.32</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>26100</v>
+        <v>269000</v>
       </c>
       <c r="K25" t="n">
-        <v>26350</v>
+        <v>258000</v>
       </c>
       <c r="L25" t="n">
-        <v>30300</v>
+        <v>261500</v>
       </c>
       <c r="M25" t="n">
-        <v>25300</v>
+        <v>256500</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>347045666900</v>
+        <v>3188291121500</v>
       </c>
       <c r="P25" t="n">
-        <v>39350</v>
+        <v>374500</v>
       </c>
       <c r="Q25" t="n">
-        <v>8200</v>
+        <v>72100</v>
       </c>
       <c r="R25" t="n">
-        <v>2000</v>
+        <v>-2983000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-1179000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
+          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['주포', '탈출 기회', '외인 유입']</t>
+          <t>['반도체', '주가 부진', '증권 뉴스']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3535</v>
+        <v>14040</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
-        <v>172</v>
+        <v>740</v>
       </c>
       <c r="H26" t="n">
-        <v>0.73</v>
+        <v>5.98</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,91 +2803,91 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3620</v>
+        <v>14600</v>
       </c>
       <c r="K26" t="n">
-        <v>3725</v>
+        <v>14800</v>
       </c>
       <c r="L26" t="n">
-        <v>3915</v>
+        <v>14950</v>
       </c>
       <c r="M26" t="n">
-        <v>3520</v>
+        <v>13910</v>
       </c>
       <c r="N26" t="n">
-        <v>1.54</v>
+        <v>6.09</v>
       </c>
       <c r="O26" t="n">
-        <v>49269130611</v>
+        <v>122101444155</v>
       </c>
       <c r="P26" t="n">
-        <v>4335</v>
+        <v>30200</v>
       </c>
       <c r="Q26" t="n">
-        <v>1246</v>
+        <v>3540</v>
       </c>
       <c r="R26" t="n">
-        <v>-110000</v>
+        <v>-236000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-163000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원전 섹터 관련 기대감에도 불구하고 모건의 대규모 매도 물량 출현 가능성 및 단기 과열 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전', '매도', '단기과열']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>259500</v>
+        <v>15040</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="F27" t="n">
-        <v>498</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>1766</v>
+        <v>370</v>
       </c>
       <c r="H27" t="n">
-        <v>46.71</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,60 +2895,60 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>269000</v>
+        <v>15640</v>
       </c>
       <c r="K27" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>261500</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>256500</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3131035541000</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-2983000</v>
+        <v>23000</v>
       </c>
       <c r="S27" t="n">
-        <v>-1179000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['반도체', '주가 부진', '증권 뉴스']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14160</v>
+        <v>14150</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.93%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>-0.39</v>
       </c>
       <c r="E28" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F28" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G28" t="n">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="H28" t="n">
         <v>2.5</v>
@@ -3002,7 +3002,7 @@
         <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>66717177375</v>
+        <v>68546483500</v>
       </c>
       <c r="P28" t="n">
         <v>31500</v>
@@ -3011,10 +3011,10 @@
         <v>1272</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>-303000</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-28000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3047,123 +3047,123 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14020</v>
+        <v>193600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29" t="n">
-        <v>726</v>
+        <v>177</v>
       </c>
       <c r="H29" t="n">
-        <v>5.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14600</v>
+        <v>203000</v>
       </c>
       <c r="K29" t="n">
-        <v>14800</v>
+        <v>195000</v>
       </c>
       <c r="L29" t="n">
-        <v>14950</v>
+        <v>195600</v>
       </c>
       <c r="M29" t="n">
-        <v>13910</v>
+        <v>191000</v>
       </c>
       <c r="N29" t="n">
-        <v>6.09</v>
+        <v>75.92</v>
       </c>
       <c r="O29" t="n">
-        <v>119831835320</v>
+        <v>553936193350</v>
       </c>
       <c r="P29" t="n">
-        <v>30200</v>
+        <v>243500</v>
       </c>
       <c r="Q29" t="n">
-        <v>3540</v>
+        <v>58600</v>
       </c>
       <c r="R29" t="n">
-        <v>-236000</v>
+        <v>-1193000</v>
       </c>
       <c r="S29" t="n">
-        <v>-163000</v>
+        <v>-48000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>원전 관련 언급 다수, 일부 투자자들은 긍정적 전망. 모건 등 기관 매매 동향 언급.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['원전', '120일선', '모건']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12220</v>
+        <v>9280</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-6.22%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>115</v>
+        <v>309</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>13030</v>
+        <v>9800</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.14</v>
+        <v>4.42</v>
       </c>
       <c r="O30" t="n">
-        <v>68550000000</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3195,14 +3195,14 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-105000</v>
+        <v>-88000</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,99 +3224,99 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>232500</v>
+        <v>12220</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-6.22%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.96</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
-        <v>268</v>
+        <v>113</v>
       </c>
       <c r="F31" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>905</v>
+        <v>122</v>
       </c>
       <c r="H31" t="n">
-        <v>7.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>253000</v>
+        <v>13030</v>
       </c>
       <c r="K31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8.539999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="O31" t="n">
-        <v>236628127500</v>
+        <v>69766000000</v>
       </c>
       <c r="P31" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-485000</v>
+        <v>-105000</v>
       </c>
       <c r="S31" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 불만과 주가 하락에 대한 우려 표현. TC 본더 수출 데이터 및 기관 매수세 언급.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['한미반도체', '공매도', 'TC본더']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>012210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_15.xlsx
+++ b/data/trending_integrated_20260911_15.xlsx
@@ -581,10 +581,10 @@
         <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208537899125</v>
+        <v>208558198965</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,7 +619,7 @@
         <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H3" t="n">
         <v>1.32</v>
@@ -702,7 +702,7 @@
         <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>8156975284</v>
+        <v>8157647124</v>
       </c>
       <c r="P3" t="n">
         <v>8150</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2615</v>
+        <v>2620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.48%</t>
+          <t>+23.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
         <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2725</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>127710000000</v>
+        <v>128699809084</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
         <v>-1952000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>거래량은 증가하나 종목 자체의 힘 부족으로 상승 동력 약화. 외국인 매도세 출현.</t>
+          <t>거래량 대비 저조한 상승세 및 주포 부재에 대한 실망감. 장기 투자 의견.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['거래량', '매도세', '손바뀜']</t>
+          <t>['주포', '거래량', '장투']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14610</v>
+        <v>137400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+20.84%</t>
+          <t>+18.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>514</v>
+        <v>172</v>
       </c>
       <c r="F5" t="n">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="G5" t="n">
-        <v>1079</v>
+        <v>372</v>
       </c>
       <c r="H5" t="n">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12090</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>219004000000</v>
+        <v>539115524350</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
-        <v>-339000</v>
+        <v>39000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
+          <t>반도체 부품 품절 이슈 및 주가 상승 기대감. 거래량 부진에 대한 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
+          <t>['반도체 부품', '품절', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137200</v>
+        <v>15710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.97%</t>
+          <t>+17.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="F6" t="n">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>367</v>
+        <v>209</v>
       </c>
       <c r="H6" t="n">
-        <v>4.32</v>
+        <v>1.24</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>116300</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.58</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>535004000000</v>
+        <v>182897000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,23 +987,23 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>39000</v>
+        <v>6000</v>
       </c>
       <c r="S6" t="n">
-        <v>118000</v>
+        <v>115000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 부품 품절 이슈 및 주가 상승 기대감. 거래량 부진에 대한 언급.</t>
+          <t>외인·기관 매수세 유입에도 얇은 호가창으로 인한 불안감. K-뷰티 대장주 등극 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체 부품', '품절', '거래량']</t>
+          <t>['K-뷰티', '외인기관', '호가창']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15710</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.77%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.19</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>528</v>
       </c>
       <c r="H7" t="n">
-        <v>1.24</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13340</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>181822000000</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>K-뷰티 대장주 등극 기대감 속 개인 투자자 중심의 상승세 전망. 다만, 외인/기관 매수에도 얇은 호가창 우려.</t>
+          <t>주가 상승 저해 요인 언급 및 지루한 공방전. 기관 매수 가능성 및 대차 거래 동향.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['K-뷰티', '대장주', '호가창']</t>
+          <t>['주가', '기관', '대차']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7210</v>
+        <v>7190</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.74%</t>
+          <t>+7.31%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6570</v>
+        <v>6700</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N8" t="n">
         <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>175473000000</v>
+        <v>176139417510</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
         <v>170000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 섹터 내 대장주로서의 기대감. 공매도 물량 증가 언급.</t>
+          <t>광통신·위성네트워크 관련주로서의 부각 및 대규모 계약 발표 기대감. 공매도 세력의 움직임.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '위성 네트워크', '대장주']</t>
+          <t>['광통신', '위성네트워크', '계약']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7680</v>
+        <v>1878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+6.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>520</v>
+        <v>270</v>
       </c>
       <c r="H9" t="n">
-        <v>11.72</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7100</v>
+        <v>1760</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>11.62</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>47118000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1263,23 +1263,23 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>45000</v>
+        <v>-445000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신영 창구 매물 및 대차 증가에 대한 우려, 금호타이어 주가 상승 기대감과 지루한 공방전.</t>
+          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신영 창구', '대차', '금호타이어']</t>
+          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1878</v>
+        <v>7870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.70%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>264</v>
+        <v>151</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>0.52</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1760</v>
+        <v>7690</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7670</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>7450</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>0.46</v>
       </c>
       <c r="O10" t="n">
-        <v>46641000000</v>
+        <v>90307319510</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="R10" t="n">
-        <v>-445000</v>
+        <v>14000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
+          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
+          <t>['품절주', '주가 조정', '유통 물량']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253000</v>
+        <v>19890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.96</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>956</v>
+        <v>655</v>
       </c>
       <c r="H11" t="n">
-        <v>7.58</v>
+        <v>10.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.539999999999999</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>152322000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,27 +1447,27 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-485000</v>
+        <v>28000</v>
       </c>
       <c r="S11" t="n">
         <v>-43000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 세력의 거센 압박 속에서 주가 하락. 개미 투자자 매수세 미흡 및 기관의 제한적 매수.</t>
+          <t>대차 해지 독려 및 공매도 세력에 대한 비판. NH증권의 목표가 상향 소식.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '개미', '기관']</t>
+          <t>['대차해지', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90600</v>
+        <v>3870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>-0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>261</v>
+        <v>95</v>
       </c>
       <c r="F12" t="n">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>1009</v>
+        <v>220</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89900</v>
+        <v>3810</v>
       </c>
       <c r="K12" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>91100</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>198178706700</v>
+        <v>99620000000</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-313000</v>
+        <v>-560000</v>
       </c>
       <c r="S12" t="n">
-        <v>77000</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>한국-미국 에너지 투자 협상 타결 및 대규모 수주 잔고 기반 원전 사업 수혜 기대감. WSJ 보도 및 연기금 매수세 유입.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19890</v>
+        <v>90800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>179</v>
+        <v>271</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="G13" t="n">
-        <v>637</v>
+        <v>1037</v>
       </c>
       <c r="H13" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19750</v>
+        <v>89900</v>
       </c>
       <c r="K13" t="n">
-        <v>19500</v>
+        <v>88700</v>
       </c>
       <c r="L13" t="n">
-        <v>20150</v>
+        <v>91100</v>
       </c>
       <c r="M13" t="n">
-        <v>19060</v>
+        <v>88000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>23.65</v>
       </c>
       <c r="O13" t="n">
-        <v>150563293750</v>
+        <v>221573508300</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>28000</v>
+        <v>-313000</v>
       </c>
       <c r="S13" t="n">
-        <v>-43000</v>
+        <v>77000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차 해지 및 공매도 세력에 대한 경고. 원전 사업 투자 기대감 및 목표가 상향 뉴스 언급.</t>
+          <t>미국과의 에너지 투자 협상 타결 및 원전 사업 수주 기대감. 수주 잔고 확대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '원전 사업']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,222 +1660,222 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>416000</v>
+        <v>14610</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>3.11</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>519</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="G14" t="n">
-        <v>311</v>
+        <v>1106</v>
       </c>
       <c r="H14" t="n">
-        <v>38.02</v>
+        <v>3.14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>415500</v>
+        <v>14510</v>
       </c>
       <c r="K14" t="n">
-        <v>407000</v>
+        <v>17010</v>
       </c>
       <c r="L14" t="n">
-        <v>418500</v>
+        <v>17310</v>
       </c>
       <c r="M14" t="n">
-        <v>404000</v>
+        <v>14600</v>
       </c>
       <c r="N14" t="n">
-        <v>37.82</v>
+        <v>0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>75302296250</v>
+        <v>220729487960</v>
       </c>
       <c r="P14" t="n">
-        <v>822000</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>283000</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>31000</v>
+        <v>-339000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8300</v>
+        <v>51900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.12</v>
+        <v>-0.44</v>
       </c>
       <c r="E15" t="n">
-        <v>316</v>
+        <v>112</v>
       </c>
       <c r="F15" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>1499</v>
+        <v>237</v>
       </c>
       <c r="H15" t="n">
-        <v>1.29</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8300</v>
+        <v>51800</v>
       </c>
       <c r="K15" t="n">
-        <v>8400</v>
+        <v>51300</v>
       </c>
       <c r="L15" t="n">
-        <v>8700</v>
+        <v>54500</v>
       </c>
       <c r="M15" t="n">
-        <v>7540</v>
+        <v>51300</v>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>3.36</v>
       </c>
       <c r="O15" t="n">
-        <v>36666251160</v>
+        <v>113241014250</v>
       </c>
       <c r="P15" t="n">
-        <v>21500</v>
+        <v>87700</v>
       </c>
       <c r="Q15" t="n">
-        <v>2300</v>
+        <v>17210</v>
       </c>
       <c r="R15" t="n">
-        <v>-183000</v>
+        <v>127000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>페니트리움 임상 시험 디자인 및 파이프라인 로드맵 언급. 9월 14일 WCLC 학회 이후 주가 대폭등 예고 및 외국계 증권사 매수 동향.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['페니트리움', '임상시험', 'WCLC']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8940</v>
+        <v>415500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="H16" t="n">
-        <v>27.19</v>
+        <v>38.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,143 +1883,143 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8970</v>
+        <v>415500</v>
       </c>
       <c r="K16" t="n">
-        <v>8780</v>
+        <v>407000</v>
       </c>
       <c r="L16" t="n">
-        <v>8950</v>
+        <v>418500</v>
       </c>
       <c r="M16" t="n">
-        <v>8680</v>
+        <v>404000</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>37.82</v>
       </c>
       <c r="O16" t="n">
-        <v>21644951220</v>
+        <v>83018131250</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>822000</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>283000</v>
       </c>
       <c r="R16" t="n">
-        <v>-8000</v>
+        <v>31000</v>
       </c>
       <c r="S16" t="n">
-        <v>-241000</v>
+        <v>5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장 관련 뉴스. 미래 기술 공개.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['로봇', '수주', '관절부품']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50400</v>
+        <v>8290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="E17" t="n">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>661</v>
+        <v>1622</v>
       </c>
       <c r="H17" t="n">
-        <v>38.78</v>
+        <v>1.29</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>50800</v>
+        <v>8300</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N17" t="n">
-        <v>38.69</v>
+        <v>1.17</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>37079640300</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>-172000</v>
+        <v>-183000</v>
       </c>
       <c r="S17" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
+          <t>임상 시험 디자인 및 파이프라인 로드맵 공개 기대감. 외국계 증권사 수급 동향.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '공시', '삼성']</t>
+          <t>['임상', '파이프라인', '로드맵']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3870</v>
+        <v>8900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>220</v>
+        <v>332</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3925</v>
+        <v>8950</v>
       </c>
       <c r="K18" t="n">
-        <v>3810</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4180</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3760</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>99172362539</v>
+        <v>22696000000</v>
       </c>
       <c r="P18" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-560000</v>
+        <v>-8000</v>
       </c>
       <c r="S18" t="n">
-        <v>14000</v>
+        <v>-241000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29000</v>
+        <v>50400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="G19" t="n">
-        <v>189</v>
+        <v>680</v>
       </c>
       <c r="H19" t="n">
-        <v>51.46</v>
+        <v>38.78</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,235 +2159,235 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29550</v>
+        <v>50800</v>
       </c>
       <c r="K19" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>29050</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>24.99</v>
+        <v>38.69</v>
       </c>
       <c r="O19" t="n">
-        <v>60123690225</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>599000</v>
+        <v>-172000</v>
       </c>
       <c r="S19" t="n">
-        <v>-270000</v>
+        <v>64000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['수주', '공시', '삼성']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25600</v>
+        <v>29550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>374</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>578</v>
+        <v>191</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32</v>
+        <v>25.55</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>26100</v>
+        <v>29800</v>
       </c>
       <c r="K20" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>25300</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.33</v>
+        <v>24.99</v>
       </c>
       <c r="O20" t="n">
-        <v>350885932200</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2000</v>
+        <v>599000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-270000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주포', '탈출 기회', '외인 유입']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1812000</v>
+        <v>25550</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>380</v>
       </c>
       <c r="F21" t="n">
-        <v>455</v>
+        <v>176</v>
       </c>
       <c r="G21" t="n">
-        <v>2095</v>
+        <v>596</v>
       </c>
       <c r="H21" t="n">
-        <v>50.55</v>
+        <v>0.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1856000</v>
+        <v>26100</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="N21" t="n">
-        <v>50.67</v>
+        <v>0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>4225538000000</v>
+        <v>352183131250</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>이란-미국 회담 및 휴전 선언 등 지정학적 이벤트에 따른 유가 하락 및 반도체 섹터 회복 기대감. AI 시대 반도체 필수론 제기.</t>
+          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '지정학적']</t>
+          <t>['주포', '탈출 기회', '외인 유입']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,46 +2396,46 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7800</v>
+        <v>193300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="H22" t="n">
-        <v>0.52</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7990</v>
+        <v>197500</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.46</v>
+        <v>75.92</v>
       </c>
       <c r="O22" t="n">
-        <v>90003000000</v>
+        <v>574118000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,67 +2459,67 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>14000</v>
+        <v>-1193000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['품절주', '주가 조정', '유통 물량']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51800</v>
+        <v>1812000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.44</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>451</v>
       </c>
       <c r="G23" t="n">
-        <v>229</v>
+        <v>2089</v>
       </c>
       <c r="H23" t="n">
-        <v>2.92</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>53200</v>
+        <v>1856000</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.36</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4688140000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2551,67 +2551,67 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>127000</v>
+        <v>-393000</v>
       </c>
       <c r="S23" t="n">
-        <v>34000</v>
+        <v>-178000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>중동 평화 회담 및 미 증시 영향에 따른 반등 기대감. CPI 발표 관련 불확실성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['CPI', '중동', '기관매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3515</v>
+        <v>12290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.90%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3620</v>
+        <v>12630</v>
       </c>
       <c r="K24" t="n">
-        <v>3725</v>
+        <v>12520</v>
       </c>
       <c r="L24" t="n">
-        <v>3915</v>
+        <v>12930</v>
       </c>
       <c r="M24" t="n">
-        <v>3507</v>
+        <v>11900</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>0.14</v>
       </c>
       <c r="O24" t="n">
-        <v>50167741605</v>
+        <v>70410067230</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>20850</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>4020</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-105000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,169 +2672,169 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>260000</v>
+        <v>3515</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>497</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
-        <v>1793</v>
+        <v>182</v>
       </c>
       <c r="H25" t="n">
-        <v>46.71</v>
+        <v>0.73</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>269000</v>
+        <v>3620</v>
       </c>
       <c r="K25" t="n">
-        <v>258000</v>
+        <v>3725</v>
       </c>
       <c r="L25" t="n">
-        <v>261500</v>
+        <v>3915</v>
       </c>
       <c r="M25" t="n">
-        <v>256500</v>
+        <v>3507</v>
       </c>
       <c r="N25" t="n">
-        <v>46.81</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>3188291121500</v>
+        <v>50404589335</v>
       </c>
       <c r="P25" t="n">
-        <v>374500</v>
+        <v>4335</v>
       </c>
       <c r="Q25" t="n">
-        <v>72100</v>
+        <v>1246</v>
       </c>
       <c r="R25" t="n">
-        <v>-2983000</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-1179000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['반도체', '주가 부진', '증권 뉴스']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14040</v>
+        <v>259500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>130</v>
+        <v>800</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>493</v>
       </c>
       <c r="G26" t="n">
-        <v>740</v>
+        <v>1831</v>
       </c>
       <c r="H26" t="n">
-        <v>5.98</v>
+        <v>46.71</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14600</v>
+        <v>269000</v>
       </c>
       <c r="K26" t="n">
-        <v>14800</v>
+        <v>258000</v>
       </c>
       <c r="L26" t="n">
-        <v>14950</v>
+        <v>261500</v>
       </c>
       <c r="M26" t="n">
-        <v>13910</v>
+        <v>256500</v>
       </c>
       <c r="N26" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="O26" t="n">
-        <v>122101444155</v>
+        <v>3602177532500</v>
       </c>
       <c r="P26" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q26" t="n">
-        <v>3540</v>
+        <v>72100</v>
       </c>
       <c r="R26" t="n">
-        <v>-236000</v>
+        <v>-2983000</v>
       </c>
       <c r="S26" t="n">
-        <v>-163000</v>
+        <v>-1179000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 기대감에도 불구하고 모건의 대규모 매도 물량 출현 가능성 및 단기 과열 우려.</t>
+          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['원전', '매도', '단기과열']</t>
+          <t>['반도체', '주가 부진', '증권 뉴스']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,283 +2856,283 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15040</v>
+        <v>14050</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E27" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G27" t="n">
-        <v>370</v>
+        <v>747</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>15640</v>
+        <v>14600</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>14950</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>13910</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>123060230205</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R27" t="n">
-        <v>23000</v>
+        <v>-236000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-163000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>원전 섹터 관련 기대감에도 불구하고 모건의 대규모 매도 물량 출현 가능성 및 단기 과열 우려.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['원전', '매도', '단기과열']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14150</v>
+        <v>15040</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="F28" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G28" t="n">
-        <v>469</v>
+        <v>362</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>14740</v>
+        <v>15640</v>
       </c>
       <c r="K28" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>14560</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>14030</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>68546483500</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-303000</v>
+        <v>23000</v>
       </c>
       <c r="S28" t="n">
-        <v>-28000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>대한민국 주식 시장에 대한 부정적 언급과 함께 향후 상승 기대감 표현. 오라클 순이익 급증 및 금리 인상 언급.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['대한광통신', '금리인상', '오라클']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>193600</v>
+        <v>14150</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-4.63%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E29" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="F29" t="n">
         <v>66</v>
       </c>
       <c r="G29" t="n">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="H29" t="n">
-        <v>75.98999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>203000</v>
+        <v>14740</v>
       </c>
       <c r="K29" t="n">
-        <v>195000</v>
+        <v>14050</v>
       </c>
       <c r="L29" t="n">
-        <v>195600</v>
+        <v>14560</v>
       </c>
       <c r="M29" t="n">
-        <v>191000</v>
+        <v>14030</v>
       </c>
       <c r="N29" t="n">
-        <v>75.92</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>553936193350</v>
+        <v>69724711550</v>
       </c>
       <c r="P29" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q29" t="n">
-        <v>58600</v>
+        <v>1272</v>
       </c>
       <c r="R29" t="n">
-        <v>-1193000</v>
+        <v>-303000</v>
       </c>
       <c r="S29" t="n">
-        <v>-48000</v>
+        <v>-28000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>대한민국 주식 시장에 대한 부정적 언급과 함께 향후 상승 기대감 표현. 오라클 순이익 급증 및 금리 인상 언급.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['대한광통신', '금리인상', '오라클']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -3154,13 +3154,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H30" t="n">
         <v>4.49</v>
@@ -3231,92 +3231,92 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12220</v>
+        <v>231000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-6.22%</t>
+          <t>-8.70%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.8</v>
+        <v>-0.96</v>
       </c>
       <c r="E31" t="n">
-        <v>113</v>
+        <v>275</v>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="G31" t="n">
-        <v>122</v>
+        <v>993</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>13030</v>
+        <v>253000</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N31" t="n">
-        <v>0.14</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>69766000000</v>
+        <v>258389474250</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R31" t="n">
-        <v>-105000</v>
+        <v>-485000</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>공매도 세력의 거센 압박 속에서 주가 하락. 개미 투자자 매수세 미흡 및 기관의 제한적 매수.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['공매도', '개미', '기관']</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042700</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_15.xlsx
+++ b/data/trending_integrated_20260911_15.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F2" t="n">
         <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>208558198965</v>
+        <v>208569000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-71000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황 발언 기반 AI 다음 핵심 시장으로 사이버 보안 부상. 엑스게이트의 양자 보안 기술 상용화 및 공급 계약 공시로 인한 급등 전망.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목. 세계 최초 양자 보안 기술 상용화 성공 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '젠슨황']</t>
+          <t>['양자 보안', '사이버 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2720</v>
+        <v>2620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.83%</t>
+          <t>+22.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
-        <v>440</v>
+        <v>245</v>
       </c>
       <c r="H3" t="n">
-        <v>1.32</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2095</v>
+        <v>2135</v>
       </c>
       <c r="K3" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>8157647124</v>
+        <v>128733000000</v>
       </c>
       <c r="P3" t="n">
-        <v>8150</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>219000</v>
+        <v>-1952000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
+          <t>높은 거래량에도 불구하고 주가 상승 동력 부족. 주포의 힘없음 및 외인 매도에 대한 실망감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
+          <t>['거래량', '주포', '외인 매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>14610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.29%</t>
+          <t>+20.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E4" t="n">
-        <v>142</v>
+        <v>529</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>284</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>1120</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>12090</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>0.03</v>
       </c>
       <c r="O4" t="n">
-        <v>128699809084</v>
+        <v>220782000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1952000</v>
+        <v>-339000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>거래량 대비 저조한 상승세 및 주포 부재에 대한 실망감. 장기 투자 의견.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '장투']</t>
+          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137400</v>
+        <v>15710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.76%</t>
+          <t>+19.38%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="E5" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="F5" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>372</v>
+        <v>211</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>1.24</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>13160</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>12910</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>16920</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>12910</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>539115524350</v>
+        <v>182940634275</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>61700</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>6750</v>
       </c>
       <c r="R5" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 부품 품절 이슈 및 주가 상승 기대감. 거래량 부진에 대한 언급.</t>
+          <t>외인·기관 매수세 유입에도 얇은 호가창으로 인한 불안감. K-뷰티 대장주 등극 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 부품', '품절', '거래량']</t>
+          <t>['K-뷰티', '외인기관', '호가창']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15710</v>
+        <v>137400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.77%</t>
+          <t>+18.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.19</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>373</v>
       </c>
       <c r="H6" t="n">
-        <v>1.24</v>
+        <v>4.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>115700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N6" t="n">
-        <v>1.43</v>
+        <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>182897000000</v>
+        <v>539252512150</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R6" t="n">
-        <v>6000</v>
+        <v>39000</v>
       </c>
       <c r="S6" t="n">
-        <v>115000</v>
+        <v>118000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인·기관 매수세 유입에도 얇은 호가창으로 인한 불안감. K-뷰티 대장주 등극 기대감.</t>
+          <t>반도체 부품 품절 이슈 및 주가 상승 기대감. 거래량 부진에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['K-뷰티', '외인기관', '호가창']</t>
+          <t>['반도체 부품', '품절', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,46 +1016,46 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>8290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+11.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>158</v>
+        <v>340</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="G7" t="n">
-        <v>528</v>
+        <v>1717</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>37102000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>-183000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 상승 저해 요인 언급 및 지루한 공방전. 기관 매수 가능성 및 대차 거래 동향.</t>
+          <t>임상 시험 디자인 및 파이프라인 로드맵 공개. 제약 바이오 섹터의 급등세와 연계된 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가', '기관', '대차']</t>
+          <t>['임상 시험', '파이프라인', '제약 바이오']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1123,20 +1123,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.31%</t>
+          <t>+9.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G8" t="n">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K8" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>176139417510</v>
+        <v>176180000000</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>170000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신·위성네트워크 관련주로서의 부각 및 대규모 계약 발표 기대감. 공매도 세력의 움직임.</t>
+          <t>광통신 및 위성네트워크 액티브 펀드 편입 소식. 폭발적인 계약 발표 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '계약']</t>
+          <t>['광통신', '위성네트워크', '계약 발표']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H9" t="n">
         <v>2.44</v>
@@ -1254,7 +1254,7 @@
         <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>47118000000</v>
+        <v>47124000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1263,23 +1263,23 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-445000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주 기대감. VLCC 용선료 폭등 뉴스 언급.</t>
+          <t>홍해 사태 및 유가 급등으로 인한 전쟁 테마주 부각. VLCC 용선료 폭등 관련 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
+          <t>['홍해 사태', '유가 상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7870</v>
+        <v>3870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="H10" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7690</v>
+        <v>3810</v>
       </c>
       <c r="K10" t="n">
-        <v>7670</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9170</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7450</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.46</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>90307319510</v>
+        <v>99650000000</v>
       </c>
       <c r="P10" t="n">
-        <v>9170</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>-560000</v>
+      </c>
+      <c r="S10" t="n">
         <v>14000</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['품절주', '주가 조정', '유통 물량']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19890</v>
+        <v>51000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G11" t="n">
-        <v>655</v>
+        <v>686</v>
       </c>
       <c r="H11" t="n">
-        <v>10.65</v>
+        <v>38.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19450</v>
+        <v>50400</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>38.69</v>
       </c>
       <c r="O11" t="n">
-        <v>152322000000</v>
+        <v>88852206525</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>28000</v>
+        <v>-172000</v>
       </c>
       <c r="S11" t="n">
-        <v>-43000</v>
+        <v>64000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차 해지 독려 및 공매도 세력에 대한 비판. NH증권의 목표가 상향 소식.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가']</t>
+          <t>['수주', '공시', '삼성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,46 +1476,46 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3870</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.53</v>
+        <v>-0.96</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>220</v>
+        <v>1009</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>7.58</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>250500</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>99620000000</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1539,67 +1539,67 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-560000</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>공매도 세력의 거센 압박 속에서 주가 하락. 개미 투자자 매수세 미흡 및 기관의 제한적 매수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['공매도', '개미', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90800</v>
+        <v>19890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="F13" t="n">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>1037</v>
+        <v>692</v>
       </c>
       <c r="H13" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>89900</v>
+        <v>19750</v>
       </c>
       <c r="K13" t="n">
-        <v>88700</v>
+        <v>19500</v>
       </c>
       <c r="L13" t="n">
-        <v>91100</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>88000</v>
+        <v>19060</v>
       </c>
       <c r="N13" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>221573508300</v>
+        <v>152461436230</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-313000</v>
+        <v>28000</v>
       </c>
       <c r="S13" t="n">
-        <v>77000</v>
+        <v>-43000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국과의 에너지 투자 협상 타결 및 원전 사업 수주 기대감. 수주 잔고 확대.</t>
+          <t>대차 해지를 통한 공매도 세력 저항 요구. 목표가 상향 및 2만원 안착 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지']</t>
+          <t>['대차 해지', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14610</v>
+        <v>415500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.11</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>519</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>280</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>1106</v>
+        <v>314</v>
       </c>
       <c r="H14" t="n">
-        <v>3.14</v>
+        <v>38.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14510</v>
+        <v>415500</v>
       </c>
       <c r="K14" t="n">
-        <v>17010</v>
+        <v>407000</v>
       </c>
       <c r="L14" t="n">
-        <v>17310</v>
+        <v>418500</v>
       </c>
       <c r="M14" t="n">
-        <v>14600</v>
+        <v>404000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03</v>
+        <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>220729487960</v>
+        <v>83018546750</v>
       </c>
       <c r="P14" t="n">
-        <v>36200</v>
+        <v>822000</v>
       </c>
       <c r="Q14" t="n">
-        <v>8920</v>
+        <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>-339000</v>
+        <v>31000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
+          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장 관련 뉴스. 미래 기술 공개.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국제 유가', '전쟁 테마주', 'WTI 100달러']</t>
+          <t>['로봇', '수주', '관절부품']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51900</v>
+        <v>8900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.44</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>237</v>
+        <v>350</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>27.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51800</v>
+        <v>8950</v>
       </c>
       <c r="K15" t="n">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>54500</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.36</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>113241014250</v>
+        <v>22706000000</v>
       </c>
       <c r="P15" t="n">
-        <v>87700</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17210</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>127000</v>
+        <v>-8000</v>
       </c>
       <c r="S15" t="n">
-        <v>34000</v>
+        <v>-241000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>415500</v>
+        <v>29550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="H16" t="n">
-        <v>38.02</v>
+        <v>25.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,143 +1883,143 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>415500</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>418500</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>37.82</v>
+        <v>24.99</v>
       </c>
       <c r="O16" t="n">
-        <v>83018131250</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>31000</v>
+        <v>599000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>-270000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장 관련 뉴스. 미래 기술 공개.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '관절부품']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8290</v>
+        <v>90800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>333</v>
+        <v>268</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G17" t="n">
-        <v>1622</v>
+        <v>1072</v>
       </c>
       <c r="H17" t="n">
-        <v>1.29</v>
+        <v>23.59</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8300</v>
+        <v>91700</v>
       </c>
       <c r="K17" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.17</v>
+        <v>23.65</v>
       </c>
       <c r="O17" t="n">
-        <v>37079640300</v>
+        <v>221590000000</v>
       </c>
       <c r="P17" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-183000</v>
+        <v>-313000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>임상 시험 디자인 및 파이프라인 로드맵 공개 기대감. 외국계 증권사 수급 동향.</t>
+          <t>미국 대규모 원전 투자 협상 임박 소식에 따른 수혜 기대. 1000억 달러 규모의 에너지 사업 합의 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['임상', '파이프라인', '로드맵']</t>
+          <t>['대미 투자', '원전 사업', '수주 잔고']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,46 +2028,46 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8900</v>
+        <v>7870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>332</v>
+        <v>151</v>
       </c>
       <c r="H18" t="n">
-        <v>27.19</v>
+        <v>0.52</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8950</v>
+        <v>7990</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>27.16</v>
+        <v>0.46</v>
       </c>
       <c r="O18" t="n">
-        <v>22696000000</v>
+        <v>90352000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,23 +2091,23 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-241000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>주가 조정 후 상승 기대감 및 품절주 특성에 대한 언급. 일부 하락 예측 의견 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['품절주', '주가 조정', '유통 물량']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50400</v>
+        <v>1812000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E19" t="n">
-        <v>186</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>95</v>
+        <v>448</v>
       </c>
       <c r="G19" t="n">
-        <v>680</v>
+        <v>2075</v>
       </c>
       <c r="H19" t="n">
-        <v>38.78</v>
+        <v>50.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>50800</v>
+        <v>1856000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38.69</v>
+        <v>50.67</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4688274000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2183,27 +2183,27 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-172000</v>
+        <v>-393000</v>
       </c>
       <c r="S19" t="n">
-        <v>64000</v>
+        <v>-178000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시 확인 및 이에 따른 주가 상승 기대.</t>
+          <t>중동 평화 회담 및 유가 하락 속 기관 매수세 유입. 계단식 상승 및 220 돌파 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['수주', '공시', '삼성']</t>
+          <t>['중동 평화', '기관 매수', '계단식 상승']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29550</v>
+        <v>51800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="H20" t="n">
-        <v>25.55</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29800</v>
+        <v>53200</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>24.99</v>
+        <v>3.36</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2275,14 +2275,14 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>599000</v>
+        <v>127000</v>
       </c>
       <c r="S20" t="n">
-        <v>-270000</v>
+        <v>34000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25550</v>
+        <v>12290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
-        <v>380</v>
+        <v>115</v>
       </c>
       <c r="F21" t="n">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>596</v>
+        <v>131</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,99 +2343,99 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26100</v>
+        <v>12630</v>
       </c>
       <c r="K21" t="n">
-        <v>26350</v>
+        <v>12520</v>
       </c>
       <c r="L21" t="n">
-        <v>30300</v>
+        <v>12930</v>
       </c>
       <c r="M21" t="n">
-        <v>25300</v>
+        <v>11900</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="O21" t="n">
-        <v>352183131250</v>
+        <v>70473508210</v>
       </c>
       <c r="P21" t="n">
-        <v>39350</v>
+        <v>20850</v>
       </c>
       <c r="Q21" t="n">
-        <v>8200</v>
+        <v>4020</v>
       </c>
       <c r="R21" t="n">
-        <v>2000</v>
+        <v>-105000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주포의 등장과 탈출 기회 제공 언급, 주가 하락 및 외인 유입에 대한 혼조세.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주포', '탈출 기회', '외인 유입']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>193300</v>
+        <v>2095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>182</v>
+        <v>440</v>
       </c>
       <c r="H22" t="n">
-        <v>75.98999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>197500</v>
+        <v>2160</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>75.92</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>574118000000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,14 +2459,14 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-1193000</v>
+        <v>219000</v>
       </c>
       <c r="S22" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1812000</v>
+        <v>259500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E23" t="n">
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="G23" t="n">
-        <v>2089</v>
+        <v>1855</v>
       </c>
       <c r="H23" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1856000</v>
+        <v>269000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>261500</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N23" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O23" t="n">
-        <v>4688140000000</v>
+        <v>3602334530000</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R23" t="n">
-        <v>-393000</v>
+        <v>-2983000</v>
       </c>
       <c r="S23" t="n">
-        <v>-178000</v>
+        <v>-1179000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>중동 평화 회담 및 미 증시 영향에 따른 반등 기대감. CPI 발표 관련 불확실성.</t>
+          <t>정치적 이슈와 연계된 부정적 언급 다수. 반도체 업종 전반의 하락세에 따른 주가 부진.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['CPI', '중동', '기관매수']</t>
+          <t>['이재명 재판', '반도체 하락']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12290</v>
+        <v>14050</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G24" t="n">
-        <v>126</v>
+        <v>752</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,130 +2619,130 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>12630</v>
+        <v>14600</v>
       </c>
       <c r="K24" t="n">
-        <v>12520</v>
+        <v>14800</v>
       </c>
       <c r="L24" t="n">
-        <v>12930</v>
+        <v>14950</v>
       </c>
       <c r="M24" t="n">
-        <v>11900</v>
+        <v>13910</v>
       </c>
       <c r="N24" t="n">
-        <v>0.14</v>
+        <v>6.09</v>
       </c>
       <c r="O24" t="n">
-        <v>70410067230</v>
+        <v>123144965755</v>
       </c>
       <c r="P24" t="n">
-        <v>20850</v>
+        <v>30200</v>
       </c>
       <c r="Q24" t="n">
-        <v>4020</v>
+        <v>3540</v>
       </c>
       <c r="R24" t="n">
-        <v>-105000</v>
+        <v>-236000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-163000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
+          <t>원전 섹터 관련 기대감에도 불구하고 모건의 대규모 매도 물량 출현 가능성 및 단기 과열 우려.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '거래량']</t>
+          <t>['원전', '매도', '단기과열']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3515</v>
+        <v>15040</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.90%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
-        <v>182</v>
+        <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3620</v>
+        <v>15640</v>
       </c>
       <c r="K25" t="n">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3915</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3507</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>50404589335</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4335</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>259500</v>
+        <v>7370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-4.04%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>800</v>
+        <v>159</v>
       </c>
       <c r="F26" t="n">
-        <v>493</v>
+        <v>69</v>
       </c>
       <c r="G26" t="n">
-        <v>1831</v>
+        <v>530</v>
       </c>
       <c r="H26" t="n">
-        <v>46.71</v>
+        <v>11.72</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,38 +2803,38 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>269000</v>
+        <v>7680</v>
       </c>
       <c r="K26" t="n">
-        <v>258000</v>
+        <v>7540</v>
       </c>
       <c r="L26" t="n">
-        <v>261500</v>
+        <v>7660</v>
       </c>
       <c r="M26" t="n">
-        <v>256500</v>
+        <v>7340</v>
       </c>
       <c r="N26" t="n">
-        <v>46.81</v>
+        <v>11.62</v>
       </c>
       <c r="O26" t="n">
-        <v>3602177532500</v>
+        <v>12312220135</v>
       </c>
       <c r="P26" t="n">
-        <v>374500</v>
+        <v>8850</v>
       </c>
       <c r="Q26" t="n">
-        <v>72100</v>
+        <v>4220</v>
       </c>
       <c r="R26" t="n">
-        <v>-2983000</v>
+        <v>45000</v>
       </c>
       <c r="S26" t="n">
-        <v>-1179000</v>
+        <v>1000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>국내 증시 및 반도체 섹터 전반의 하락세 속 삼성전자 주가 부진에 대한 불만. 정치적 이슈 언급.</t>
+          <t>주가 상승 저해 요인 언급 및 지루한 공방전. 기관 매수 가능성 및 대차 거래 동향.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['반도체', '주가 부진', '증권 뉴스']</t>
+          <t>['주가', '기관', '대차']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,138 +2856,138 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14050</v>
+        <v>193300</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="F27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G27" t="n">
-        <v>747</v>
+        <v>182</v>
       </c>
       <c r="H27" t="n">
-        <v>5.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14600</v>
+        <v>203000</v>
       </c>
       <c r="K27" t="n">
-        <v>14800</v>
+        <v>195000</v>
       </c>
       <c r="L27" t="n">
-        <v>14950</v>
+        <v>195600</v>
       </c>
       <c r="M27" t="n">
-        <v>13910</v>
+        <v>191000</v>
       </c>
       <c r="N27" t="n">
-        <v>6.09</v>
+        <v>75.92</v>
       </c>
       <c r="O27" t="n">
-        <v>123060230205</v>
+        <v>574253956350</v>
       </c>
       <c r="P27" t="n">
-        <v>30200</v>
+        <v>243500</v>
       </c>
       <c r="Q27" t="n">
-        <v>3540</v>
+        <v>58600</v>
       </c>
       <c r="R27" t="n">
-        <v>-236000</v>
+        <v>-1193000</v>
       </c>
       <c r="S27" t="n">
-        <v>-163000</v>
+        <v>-48000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 기대감에도 불구하고 모건의 대규모 매도 물량 출현 가능성 및 단기 과열 우려.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['원전', '매도', '단기과열']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15040</v>
+        <v>9280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>15640</v>
+        <v>9800</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3011,14 +3011,14 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>23000</v>
+        <v>-88000</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
@@ -3055,20 +3055,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-5.41%</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>-0.39</v>
       </c>
       <c r="E29" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F29" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G29" t="n">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="H29" t="n">
         <v>2.5</v>
@@ -3079,28 +3079,28 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14740</v>
+        <v>14960</v>
       </c>
       <c r="K29" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>14560</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>14030</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>69724711550</v>
+        <v>69771000000</v>
       </c>
       <c r="P29" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>-303000</v>
@@ -3139,31 +3139,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9280</v>
+        <v>3515</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-9.06%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G30" t="n">
-        <v>310</v>
+        <v>181</v>
       </c>
       <c r="H30" t="n">
-        <v>4.49</v>
+        <v>0.73</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9800</v>
+        <v>3865</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.42</v>
+        <v>1.54</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>50417000000</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3195,14 +3195,14 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3211,11 +3211,11 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,90 +3224,90 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>231000</v>
+        <v>25550</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-8.70%</t>
+          <t>-15.68%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.96</v>
+        <v>-0.01</v>
       </c>
       <c r="E31" t="n">
-        <v>275</v>
+        <v>387</v>
       </c>
       <c r="F31" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G31" t="n">
-        <v>993</v>
+        <v>602</v>
       </c>
       <c r="H31" t="n">
-        <v>7.58</v>
+        <v>0.32</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>253000</v>
+        <v>30300</v>
       </c>
       <c r="K31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8.539999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
-        <v>258389474250</v>
+        <v>352256000000</v>
       </c>
       <c r="P31" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-485000</v>
+        <v>2000</v>
       </c>
       <c r="S31" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>공매도 세력의 거센 압박 속에서 주가 하락. 개미 투자자 매수세 미흡 및 기관의 제한적 매수.</t>
+          <t>신규 상장 이후 변동성 확대. 전설적인 종목이라는 언급과 함께 주포의 기회 제공에 대한 기대.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>['공매도', '개미', '기관']</t>
+          <t>['신규 상장', '주포', '변동성']</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
